--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\devdh\Documents\MLLM\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E369901-8417-4AB2-83A5-F7562476EFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8EE3B7-C2EF-489D-AA81-D2C4F8FF309E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C8E58A68-2853-48D5-B4A5-6617BC9E1857}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Seed</t>
   </si>
@@ -57,6 +57,12 @@
   </si>
   <si>
     <t>fish vs house, ball vs tree</t>
+  </si>
+  <si>
+    <t>tree vs car - Model answered: [next trial], tree vs baby - Model answered: car house</t>
+  </si>
+  <si>
+    <t>ball vs house, water vs baby both empty</t>
   </si>
 </sst>
 </file>
@@ -465,6 +471,13 @@
       <c r="C2">
         <v>0</v>
       </c>
+      <c r="D2">
+        <f>28/30</f>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -472,6 +485,9 @@
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -504,7 +520,11 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <f>28/30</f>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
